--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137283258</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137283259</v>
       </c>
       <c r="B4" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137283258</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137283259</v>
       </c>
       <c r="B4" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137283258</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137283259</v>
       </c>
       <c r="B4" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137283258</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137283259</v>
       </c>
       <c r="B4" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137283258</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137283259</v>
       </c>
       <c r="B4" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43346-2026 artfynd.xlsx
+++ b/artfynd/A 43346-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283257</v>
       </c>
       <c r="B2" t="n">
-        <v>92196</v>
+        <v>92200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137283258</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137283259</v>
       </c>
       <c r="B4" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
